--- a/sipii_caixa_20260708.xlsx
+++ b/sipii_caixa_20260708.xlsx
@@ -2695,42 +2695,178 @@
           <t>https://www.caixa.gov.br/fundos-investimento/e-fundos/renda-fixa-longo-prazo</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>15.154.422/0001-99</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>RF até 49% Crédito Privado</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
       <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 90%</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM9" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr"/>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA E-FUNDO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).As movimentações neste Fundo são realizadas exclusivamente pelo Internet Banking.</t>
+        </is>
+      </c>
+      <c r="AT9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AU9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AV9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AX9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AY9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AZ9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5834.pdf</t>
+        </is>
+      </c>
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr"/>
     </row>
@@ -14215,42 +14351,182 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
-      <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr"/>
-      <c r="AE54" s="2" t="inlineStr"/>
-      <c r="AF54" s="2" t="inlineStr"/>
-      <c r="AG54" s="2" t="inlineStr"/>
-      <c r="AH54" s="2" t="inlineStr"/>
-      <c r="AI54" s="2" t="inlineStr"/>
-      <c r="AJ54" s="2" t="inlineStr"/>
-      <c r="AK54" s="2" t="inlineStr"/>
-      <c r="AL54" s="2" t="inlineStr"/>
-      <c r="AM54" s="2" t="inlineStr"/>
-      <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Curto Prazo</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>CURTO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
-      <c r="AQ54" s="2" t="inlineStr"/>
-      <c r="AR54" s="2" t="inlineStr"/>
-      <c r="AS54" s="2" t="inlineStr"/>
-      <c r="AT54" s="2" t="inlineStr"/>
-      <c r="AU54" s="2" t="inlineStr"/>
-      <c r="AV54" s="2" t="inlineStr"/>
-      <c r="AW54" s="2" t="inlineStr"/>
-      <c r="AX54" s="2" t="inlineStr"/>
-      <c r="AY54" s="2" t="inlineStr"/>
-      <c r="AZ54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR54" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS54" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AT54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AU54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AV54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AW54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AX54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AY54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AZ54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
+        </is>
+      </c>
       <c r="BA54" s="2" t="inlineStr"/>
       <c r="BB54" s="2" t="inlineStr"/>
     </row>
@@ -28836,12 +29112,12 @@
       </c>
       <c r="Q111" s="4" t="inlineStr">
         <is>
-          <t>30.068.049/0001-47</t>
+          <t>59.815.671/0001-53</t>
         </is>
       </c>
       <c r="R111" s="4" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="S111" s="4" t="inlineStr">
@@ -28876,14 +29152,14 @@
       </c>
       <c r="Y111" s="4" t="inlineStr">
         <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z111" s="4" t="inlineStr">
+        <is>
           <t>D+1 (du)</t>
         </is>
       </c>
-      <c r="Z111" s="4" t="inlineStr">
-        <is>
-          <t>D+1 (du)</t>
-        </is>
-      </c>
       <c r="AA111" s="4" t="inlineStr">
         <is>
           <t>D+03 (du)</t>
@@ -28891,7 +29167,7 @@
       </c>
       <c r="AB111" s="4" t="inlineStr">
         <is>
-          <t>IBOV</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AC111" s="4" t="inlineStr">
@@ -28901,7 +29177,7 @@
       </c>
       <c r="AD111" s="4" t="inlineStr">
         <is>
-          <t>Aberto para captação</t>
+          <t>Fechado para captação</t>
         </is>
       </c>
       <c r="AE111" s="4" t="inlineStr">
@@ -28926,27 +29202,23 @@
       </c>
       <c r="AI111" s="4" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 100%</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="AJ111" s="4" t="inlineStr">
         <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AK111" s="4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="AK111" s="4" t="inlineStr"/>
       <c r="AL111" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["GOV", "Pessoa Física", "PJ Atacado", "Private"]</t>
         </is>
       </c>
       <c r="AM111" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["GOV", "Pessoa Física", "PJ Atacado", "Private"]</t>
         </is>
       </c>
       <c r="AN111" s="4" t="inlineStr">
@@ -28961,7 +29233,7 @@
       </c>
       <c r="AP111" s="4" t="inlineStr">
         <is>
-          <t>2021-06-13T00:00:00Z</t>
+          <t>2025-05-04T00:00:00Z</t>
         </is>
       </c>
       <c r="AQ111" s="4" t="inlineStr">
@@ -28971,47 +29243,47 @@
       </c>
       <c r="AR111" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SEGURIDADE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SEGURIDADE II FUNDO DE INVESTIMENTO FINANCEIRO AÇÕES - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS111" s="4" t="inlineStr">
         <is>
-          <t>Canal de distribuição: Rede CAIXA, IBC. A reserva inicial, no âmbito da OFERTA, será feita por meio do Home Broker CAIXA. Resgates: Lock up de 45 dias. Inicio dia 30/04/2021 - Termino 13/06/2021. Liberado resgate a partir do dia 14/06/2021 (segunda-feira).</t>
+          <t>Fundo ficará fechado para novas aplicações a partir do dia 13/05/2025 (inclusive).</t>
         </is>
       </c>
       <c r="AT111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6499.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7971.pdf</t>
         </is>
       </c>
       <c r="AU111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6499.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7971.pdf</t>
         </is>
       </c>
       <c r="AV111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7971.pdf</t>
         </is>
       </c>
       <c r="AW111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_7971.pdf</t>
         </is>
       </c>
       <c r="AX111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6499.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7971.pdf</t>
         </is>
       </c>
       <c r="AY111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6499.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7971.pdf</t>
         </is>
       </c>
       <c r="AZ111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7971.pdf</t>
         </is>
       </c>
       <c r="BA111" s="4" t="inlineStr"/>
@@ -30645,17 +30917,17 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-2</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-4</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>03.915.910/0001-92</t>
+          <t>03.555.959/0001-81</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
@@ -30665,29 +30937,29 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="V118" s="2" t="inlineStr">
+      <c r="W118" s="2" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr">
+      <c r="X118" s="2" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="X118" s="2" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="Y118" s="2" t="inlineStr">
         <is>
           <t>D+0 (du)</t>
@@ -30715,7 +30987,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>Aberto para captação</t>
+          <t>Fechado para captação</t>
         </is>
       </c>
       <c r="AE118" s="2" t="inlineStr">
@@ -30728,11 +31000,7 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AG118" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
+      <c r="AG118" s="2" t="inlineStr"/>
       <c r="AH118" s="2" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -30769,48 +31037,47 @@
       </c>
       <c r="AR118" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS II - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS IV - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS118" s="2" t="inlineStr">
         <is>
-          <t>O fundo encontra-se aberto para receber recursos provenientes de outros Fundos FMP-FGTS.
-Prazo de carência: 6 meses para transferência total ou parcial do investimento no FUNDO para outro FMP- FGTS ou para um Clube de Investimento – FGTS, ou 12 meses para retorno à(s) conta(s) vinculada(s) do investidor junto ao FGTS.</t>
+          <t>FUNDO FECHADO.</t>
         </is>
       </c>
       <c r="AT118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5202.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5204.pdf</t>
         </is>
       </c>
       <c r="AU118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5202.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5204.pdf</t>
         </is>
       </c>
       <c r="AV118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5202.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5204.pdf</t>
         </is>
       </c>
       <c r="AW118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5202.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5204.pdf</t>
         </is>
       </c>
       <c r="AX118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5202.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5204.pdf</t>
         </is>
       </c>
       <c r="AY118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5202.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5204.pdf</t>
         </is>
       </c>
       <c r="AZ118" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5202.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5204.pdf</t>
         </is>
       </c>
       <c r="BA118" s="2" t="inlineStr"/>
@@ -34981,12 +35248,12 @@
       </c>
       <c r="Q135" s="4" t="inlineStr">
         <is>
-          <t>09.181.268/0001-41</t>
+          <t>09.548.725/0001-93</t>
         </is>
       </c>
       <c r="R135" s="4" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="S135" s="4" t="inlineStr">
@@ -34996,12 +35263,12 @@
       </c>
       <c r="T135" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="U135" s="4" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000000.0</t>
         </is>
       </c>
       <c r="V135" s="4" t="inlineStr">
@@ -35016,7 +35283,7 @@
       </c>
       <c r="X135" s="4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y135" s="4" t="inlineStr">
@@ -35056,7 +35323,7 @@
       </c>
       <c r="AF135" s="4" t="inlineStr">
         <is>
-          <t>GERAL</t>
+          <t>QUALIFICADO</t>
         </is>
       </c>
       <c r="AG135" s="4" t="inlineStr">
@@ -35104,7 +35371,7 @@
       </c>
       <c r="AR135" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SAÚDE SUPLEMENTAR - ANS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SAUDE SUPLEMENTAR - ANS II FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS135" s="4" t="inlineStr">
@@ -35119,37 +35386,37 @@
       </c>
       <c r="AT135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5080.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5132.pdf</t>
         </is>
       </c>
       <c r="AU135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5080.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5132.pdf</t>
         </is>
       </c>
       <c r="AV135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5080.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5132.pdf</t>
         </is>
       </c>
       <c r="AW135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5080.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5132.pdf</t>
         </is>
       </c>
       <c r="AX135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5080.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5132.pdf</t>
         </is>
       </c>
       <c r="AY135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5080.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5132.pdf</t>
         </is>
       </c>
       <c r="AZ135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5080.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5132.pdf</t>
         </is>
       </c>
       <c r="BA135" s="4" t="inlineStr"/>
